--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134456766</v>
+        <v>135336952</v>
       </c>
       <c r="B3" t="n">
-        <v>79963</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623830</v>
+        <v>623805</v>
       </c>
       <c r="R3" t="n">
-        <v>7310041</v>
+        <v>7310020</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134456768</v>
+        <v>135336951</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>99217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623900</v>
+        <v>623787</v>
       </c>
       <c r="R4" t="n">
-        <v>7310120</v>
+        <v>7310002</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +958,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +988,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135330529</v>
+        <v>134456766</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623697</v>
+        <v>623830</v>
       </c>
       <c r="R5" t="n">
-        <v>7310241</v>
+        <v>7310041</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,22 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,23 +1099,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135330532</v>
+        <v>134456768</v>
       </c>
       <c r="B6" t="n">
         <v>79039</v>
@@ -1142,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623736</v>
+        <v>623900</v>
       </c>
       <c r="R6" t="n">
-        <v>7310280</v>
+        <v>7310120</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,22 +1176,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,26 +1206,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134456772</v>
+        <v>135330529</v>
       </c>
       <c r="B7" t="n">
-        <v>79452</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623724</v>
+        <v>623697</v>
       </c>
       <c r="R7" t="n">
-        <v>7310158</v>
+        <v>7310241</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,22 +1283,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,44 +1313,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134456771</v>
+        <v>135330532</v>
       </c>
       <c r="B8" t="n">
-        <v>91988</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623825</v>
+        <v>623736</v>
       </c>
       <c r="R8" t="n">
-        <v>7310297</v>
+        <v>7310280</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,22 +1394,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,22 +1424,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134456774</v>
+        <v>135336962</v>
       </c>
       <c r="B9" t="n">
-        <v>83222</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,13 +1475,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623732</v>
+        <v>623775</v>
       </c>
       <c r="R9" t="n">
-        <v>7310148</v>
+        <v>7310254</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,22 +1505,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,22 +1535,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135333617</v>
+        <v>134456772</v>
       </c>
       <c r="B10" t="n">
-        <v>83222</v>
+        <v>79452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,13 +1586,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623762</v>
+        <v>623724</v>
       </c>
       <c r="R10" t="n">
-        <v>7310114</v>
+        <v>7310158</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1604,22 +1616,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,26 +1646,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135333622</v>
+        <v>135336961</v>
       </c>
       <c r="B11" t="n">
-        <v>83222</v>
+        <v>81355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1685,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623739</v>
+        <v>623755</v>
       </c>
       <c r="R11" t="n">
-        <v>7310146</v>
+        <v>7310257</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1720,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1730,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1761,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135330534</v>
+        <v>134456771</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>91988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,13 +1804,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623725</v>
+        <v>623825</v>
       </c>
       <c r="R12" t="n">
-        <v>7310245</v>
+        <v>7310297</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1826,22 +1834,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,48 +1864,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135333620</v>
+        <v>134456774</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1911,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623771</v>
+        <v>623732</v>
       </c>
       <c r="R13" t="n">
-        <v>7310137</v>
+        <v>7310148</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,22 +1941,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,26 +1971,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135333618</v>
+        <v>135333617</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>83222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623772</v>
+        <v>623762</v>
       </c>
       <c r="R14" t="n">
-        <v>7310131</v>
+        <v>7310114</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135333623</v>
+        <v>135333622</v>
       </c>
       <c r="B15" t="n">
-        <v>78776</v>
+        <v>83222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623707</v>
+        <v>623739</v>
       </c>
       <c r="R15" t="n">
-        <v>7310261</v>
+        <v>7310146</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,32 +2205,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135333630</v>
+        <v>135330534</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>91937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623777</v>
+        <v>623725</v>
       </c>
       <c r="R16" t="n">
-        <v>7310269</v>
+        <v>7310245</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,12 +2300,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2316,32 +2316,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134456779</v>
+        <v>135333620</v>
       </c>
       <c r="B17" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623810</v>
+        <v>623771</v>
       </c>
       <c r="R17" t="n">
-        <v>7310162</v>
+        <v>7310137</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2381,22 +2381,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,22 +2411,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135333627</v>
+        <v>135333618</v>
       </c>
       <c r="B18" t="n">
-        <v>79130</v>
+        <v>78776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2458,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623753</v>
+        <v>623772</v>
       </c>
       <c r="R18" t="n">
-        <v>7310291</v>
+        <v>7310131</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2493,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2503,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134456769</v>
+        <v>135333623</v>
       </c>
       <c r="B19" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,21 +2549,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623900</v>
+        <v>623707</v>
       </c>
       <c r="R19" t="n">
-        <v>7310143</v>
+        <v>7310261</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2599,22 +2603,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,22 +2633,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134456776</v>
+        <v>135333630</v>
       </c>
       <c r="B20" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,21 +2660,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,13 +2684,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623807</v>
+        <v>623777</v>
       </c>
       <c r="R20" t="n">
-        <v>7310160</v>
+        <v>7310269</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2706,22 +2714,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,22 +2744,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134456777</v>
+        <v>134456779</v>
       </c>
       <c r="B21" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,13 +2795,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623758</v>
+        <v>623810</v>
       </c>
       <c r="R21" t="n">
-        <v>7310258</v>
+        <v>7310162</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2818,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135330531</v>
+        <v>135333627</v>
       </c>
       <c r="B22" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2866,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623713</v>
+        <v>623753</v>
       </c>
       <c r="R22" t="n">
-        <v>7310247</v>
+        <v>7310291</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2925,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,12 +2962,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2966,7 +2978,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135333621</v>
+        <v>134456769</v>
       </c>
       <c r="B23" t="n">
         <v>79992</v>
@@ -3001,13 +3013,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623770</v>
+        <v>623900</v>
       </c>
       <c r="R23" t="n">
-        <v>7310168</v>
+        <v>7310143</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3031,22 +3043,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3061,23 +3073,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135333625</v>
+        <v>134456776</v>
       </c>
       <c r="B24" t="n">
         <v>79992</v>
@@ -3112,13 +3120,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623754</v>
+        <v>623807</v>
       </c>
       <c r="R24" t="n">
-        <v>7310291</v>
+        <v>7310160</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3142,22 +3150,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,23 +3180,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135333631</v>
+        <v>134456777</v>
       </c>
       <c r="B25" t="n">
         <v>79992</v>
@@ -3223,13 +3227,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623776</v>
+        <v>623758</v>
       </c>
       <c r="R25" t="n">
-        <v>7310265</v>
+        <v>7310258</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,22 +3257,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3283,23 +3287,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135333633</v>
+        <v>135330531</v>
       </c>
       <c r="B26" t="n">
         <v>79992</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623803</v>
+        <v>623713</v>
       </c>
       <c r="R26" t="n">
-        <v>7310251</v>
+        <v>7310247</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3394,12 +3394,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3410,7 +3410,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135333636</v>
+        <v>135333621</v>
       </c>
       <c r="B27" t="n">
         <v>79992</v>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623860</v>
+        <v>623770</v>
       </c>
       <c r="R27" t="n">
-        <v>7310128</v>
+        <v>7310168</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134456770</v>
+        <v>135333625</v>
       </c>
       <c r="B28" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,21 +3532,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623875</v>
+        <v>623754</v>
       </c>
       <c r="R28" t="n">
-        <v>7310171</v>
+        <v>7310291</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3586,22 +3586,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,22 +3616,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135333628</v>
+        <v>135333631</v>
       </c>
       <c r="B29" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,21 +3643,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3663,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623755</v>
+        <v>623776</v>
       </c>
       <c r="R29" t="n">
-        <v>7310283</v>
+        <v>7310265</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3698,7 +3702,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3712,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,10 +3743,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134456773</v>
+        <v>135333633</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3750,21 +3754,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3774,13 +3778,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623744</v>
+        <v>623803</v>
       </c>
       <c r="R30" t="n">
-        <v>7310162</v>
+        <v>7310251</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3804,27 +3808,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,22 +3838,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134456775</v>
+        <v>135333636</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3862,21 +3865,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3886,13 +3889,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>623790</v>
+        <v>623860</v>
       </c>
       <c r="R31" t="n">
-        <v>7310142</v>
+        <v>7310128</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3916,27 +3919,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gamla hackmärken i tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,22 +3949,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135330530</v>
+        <v>135336953</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3974,21 +3976,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3998,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623714</v>
+        <v>623790</v>
       </c>
       <c r="R32" t="n">
-        <v>7310251</v>
+        <v>7310126</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,7 +4035,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4043,7 +4045,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,12 +4060,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4074,10 +4076,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135333626</v>
+        <v>135336958</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4085,21 +4087,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4109,13 +4111,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623753</v>
+        <v>623711</v>
       </c>
       <c r="R33" t="n">
-        <v>7310291</v>
+        <v>7310252</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4144,7 +4146,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4154,7 +4156,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4169,12 +4171,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4185,10 +4187,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134456767</v>
+        <v>135336963</v>
       </c>
       <c r="B34" t="n">
-        <v>79963</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,21 +4198,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4220,13 +4222,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623900</v>
+        <v>623802</v>
       </c>
       <c r="R34" t="n">
-        <v>7310120</v>
+        <v>7310245</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4250,22 +4252,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4280,22 +4282,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135333624</v>
+        <v>134456770</v>
       </c>
       <c r="B35" t="n">
-        <v>79963</v>
+        <v>78377</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,21 +4309,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,13 +4333,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623709</v>
+        <v>623875</v>
       </c>
       <c r="R35" t="n">
-        <v>7310261</v>
+        <v>7310171</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4357,22 +4363,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4387,26 +4393,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135333629</v>
+        <v>135333628</v>
       </c>
       <c r="B36" t="n">
-        <v>79963</v>
+        <v>78377</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4414,21 +4416,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4438,7 +4440,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>623753</v>
+        <v>623755</v>
       </c>
       <c r="R36" t="n">
         <v>7310283</v>
@@ -4514,10 +4516,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134456778</v>
+        <v>134456773</v>
       </c>
       <c r="B37" t="n">
-        <v>79396</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4527,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,13 +4551,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623793</v>
+        <v>623744</v>
       </c>
       <c r="R37" t="n">
-        <v>7310206</v>
+        <v>7310162</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4584,7 +4586,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4594,7 +4596,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4621,10 +4628,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135330533</v>
+        <v>134456775</v>
       </c>
       <c r="B38" t="n">
-        <v>79396</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4632,21 +4639,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4656,13 +4663,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623740</v>
+        <v>623790</v>
       </c>
       <c r="R38" t="n">
-        <v>7310280</v>
+        <v>7310142</v>
       </c>
       <c r="S38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4686,22 +4693,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gamla hackmärken i tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4716,15 +4728,1693 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135336954</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>623782</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7310156</v>
+      </c>
+      <c r="S39" t="n">
+        <v>7</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135336955</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>623750</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7310194</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135336960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>623741</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7310258</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135336965</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>623813</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7310236</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135330530</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>623714</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S43" t="n">
+        <v>9</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>Petya Valcheva</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>Petya Valcheva</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135333626</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134456767</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7310120</v>
+      </c>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135333624</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>623709</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7310261</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135333629</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135336957</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>623699</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7310215</v>
+      </c>
+      <c r="S48" t="n">
+        <v>8</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134456778</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>623793</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7310206</v>
+      </c>
+      <c r="S49" t="n">
+        <v>11</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135330533</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>623740</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S50" t="n">
+        <v>17</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135336956</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>623738</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7310208</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135336959</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>623723</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7310256</v>
+      </c>
+      <c r="S52" t="n">
+        <v>9</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135336964</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>623808</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7310244</v>
+      </c>
+      <c r="S53" t="n">
+        <v>9</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>rikligt med soral</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2316,7 +2316,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135333620</v>
+        <v>135331260</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2347,17 +2347,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623771</v>
+        <v>623814</v>
       </c>
       <c r="R17" t="n">
-        <v>7310137</v>
+        <v>7310091</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,12 +2411,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2427,45 +2427,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135333618</v>
+        <v>135331261</v>
       </c>
       <c r="B18" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623772</v>
+        <v>623779</v>
       </c>
       <c r="R18" t="n">
-        <v>7310131</v>
+        <v>7310157</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,12 +2522,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135333623</v>
+        <v>135333620</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623707</v>
+        <v>623771</v>
       </c>
       <c r="R19" t="n">
-        <v>7310261</v>
+        <v>7310137</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135333630</v>
+        <v>135333618</v>
       </c>
       <c r="B20" t="n">
         <v>78776</v>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623777</v>
+        <v>623772</v>
       </c>
       <c r="R20" t="n">
-        <v>7310269</v>
+        <v>7310131</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134456779</v>
+        <v>135333623</v>
       </c>
       <c r="B21" t="n">
-        <v>79130</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623810</v>
+        <v>623707</v>
       </c>
       <c r="R21" t="n">
-        <v>7310162</v>
+        <v>7310261</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2825,22 +2825,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,22 +2855,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135333627</v>
+        <v>135333630</v>
       </c>
       <c r="B22" t="n">
-        <v>79130</v>
+        <v>78776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2882,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623753</v>
+        <v>623777</v>
       </c>
       <c r="R22" t="n">
-        <v>7310291</v>
+        <v>7310269</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2937,7 +2941,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2951,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,10 +2982,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134456769</v>
+        <v>134456779</v>
       </c>
       <c r="B23" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,21 +2993,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3013,13 +3017,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623900</v>
+        <v>623810</v>
       </c>
       <c r="R23" t="n">
-        <v>7310143</v>
+        <v>7310162</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3048,7 +3052,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3058,7 +3062,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3085,10 +3089,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134456776</v>
+        <v>135333627</v>
       </c>
       <c r="B24" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3096,21 +3100,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3120,13 +3124,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623807</v>
+        <v>623753</v>
       </c>
       <c r="R24" t="n">
-        <v>7310160</v>
+        <v>7310291</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3150,22 +3154,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,19 +3184,23 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134456777</v>
+        <v>134456769</v>
       </c>
       <c r="B25" t="n">
         <v>79992</v>
@@ -3227,13 +3235,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623758</v>
+        <v>623900</v>
       </c>
       <c r="R25" t="n">
-        <v>7310258</v>
+        <v>7310143</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3262,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3272,7 +3280,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3299,7 +3307,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135330531</v>
+        <v>134456776</v>
       </c>
       <c r="B26" t="n">
         <v>79992</v>
@@ -3334,13 +3342,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623713</v>
+        <v>623807</v>
       </c>
       <c r="R26" t="n">
-        <v>7310247</v>
+        <v>7310160</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3364,22 +3372,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3394,23 +3402,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135333621</v>
+        <v>134456777</v>
       </c>
       <c r="B27" t="n">
         <v>79992</v>
@@ -3445,13 +3449,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623770</v>
+        <v>623758</v>
       </c>
       <c r="R27" t="n">
-        <v>7310168</v>
+        <v>7310258</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3475,22 +3479,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,23 +3509,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135333625</v>
+        <v>135330531</v>
       </c>
       <c r="B28" t="n">
         <v>79992</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623754</v>
+        <v>623713</v>
       </c>
       <c r="R28" t="n">
-        <v>7310291</v>
+        <v>7310247</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,12 +3616,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3632,7 +3632,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135333631</v>
+        <v>135333621</v>
       </c>
       <c r="B29" t="n">
         <v>79992</v>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623776</v>
+        <v>623770</v>
       </c>
       <c r="R29" t="n">
-        <v>7310265</v>
+        <v>7310168</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3743,7 +3743,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135333633</v>
+        <v>135333625</v>
       </c>
       <c r="B30" t="n">
         <v>79992</v>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623803</v>
+        <v>623754</v>
       </c>
       <c r="R30" t="n">
-        <v>7310251</v>
+        <v>7310291</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3854,7 +3854,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135333636</v>
+        <v>135333631</v>
       </c>
       <c r="B31" t="n">
         <v>79992</v>
@@ -3889,13 +3889,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>623860</v>
+        <v>623776</v>
       </c>
       <c r="R31" t="n">
-        <v>7310128</v>
+        <v>7310265</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3965,7 +3965,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135336953</v>
+        <v>135333633</v>
       </c>
       <c r="B32" t="n">
         <v>79992</v>
@@ -4000,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623790</v>
+        <v>623803</v>
       </c>
       <c r="R32" t="n">
-        <v>7310126</v>
+        <v>7310251</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,12 +4060,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4076,7 +4076,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135336958</v>
+        <v>135333636</v>
       </c>
       <c r="B33" t="n">
         <v>79992</v>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623711</v>
+        <v>623860</v>
       </c>
       <c r="R33" t="n">
-        <v>7310252</v>
+        <v>7310128</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4171,12 +4171,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4187,7 +4187,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135336963</v>
+        <v>135336953</v>
       </c>
       <c r="B34" t="n">
         <v>79992</v>
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623802</v>
+        <v>623790</v>
       </c>
       <c r="R34" t="n">
-        <v>7310245</v>
+        <v>7310126</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134456770</v>
+        <v>135336958</v>
       </c>
       <c r="B35" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4309,21 +4309,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4333,13 +4333,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623875</v>
+        <v>623711</v>
       </c>
       <c r="R35" t="n">
-        <v>7310171</v>
+        <v>7310252</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4363,22 +4363,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4393,22 +4393,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135333628</v>
+        <v>135336963</v>
       </c>
       <c r="B36" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4416,21 +4420,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4440,13 +4444,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>623755</v>
+        <v>623802</v>
       </c>
       <c r="R36" t="n">
-        <v>7310283</v>
+        <v>7310245</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4475,7 +4479,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4485,7 +4489,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4500,12 +4504,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4516,10 +4520,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134456773</v>
+        <v>134456770</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,21 +4531,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4551,13 +4555,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623744</v>
+        <v>623875</v>
       </c>
       <c r="R37" t="n">
-        <v>7310162</v>
+        <v>7310171</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4586,7 +4590,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4596,12 +4600,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4628,10 +4627,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134456775</v>
+        <v>135333628</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4639,21 +4638,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4663,13 +4662,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623790</v>
+        <v>623755</v>
       </c>
       <c r="R38" t="n">
-        <v>7310142</v>
+        <v>7310283</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4693,27 +4692,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Gamla hackmärken i tall</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4728,19 +4722,23 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135336954</v>
+        <v>134456773</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4769,24 +4767,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623782</v>
+        <v>623744</v>
       </c>
       <c r="R39" t="n">
-        <v>7310156</v>
+        <v>7310162</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4810,22 +4803,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4840,23 +4838,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135336955</v>
+        <v>134456775</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4885,24 +4879,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>623750</v>
+        <v>623790</v>
       </c>
       <c r="R40" t="n">
-        <v>7310194</v>
+        <v>7310142</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4926,22 +4915,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla hackmärken i tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4956,23 +4950,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135336960</v>
+        <v>135336954</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -5003,7 +4993,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5012,13 +5002,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>623741</v>
+        <v>623782</v>
       </c>
       <c r="R41" t="n">
-        <v>7310258</v>
+        <v>7310156</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5047,7 +5037,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,7 +5047,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5088,7 +5078,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135336965</v>
+        <v>135336955</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -5128,13 +5118,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>623813</v>
+        <v>623750</v>
       </c>
       <c r="R42" t="n">
-        <v>7310236</v>
+        <v>7310194</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5163,7 +5153,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5163,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5204,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135330530</v>
+        <v>135336960</v>
       </c>
       <c r="B43" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5215,37 +5205,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623714</v>
+        <v>623741</v>
       </c>
       <c r="R43" t="n">
-        <v>7310251</v>
+        <v>7310258</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5274,7 +5269,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5284,7 +5279,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5299,12 +5294,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5315,10 +5310,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135333626</v>
+        <v>135336965</v>
       </c>
       <c r="B44" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5326,37 +5321,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623753</v>
+        <v>623813</v>
       </c>
       <c r="R44" t="n">
-        <v>7310291</v>
+        <v>7310236</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,12 +5410,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5426,48 +5426,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134456767</v>
+        <v>135331264</v>
       </c>
       <c r="B45" t="n">
-        <v>79963</v>
+        <v>98060</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>623900</v>
+        <v>623755</v>
       </c>
       <c r="R45" t="n">
-        <v>7310120</v>
+        <v>7310300</v>
       </c>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5491,22 +5491,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5521,22 +5521,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135333624</v>
+        <v>135330530</v>
       </c>
       <c r="B46" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5544,21 +5548,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5568,13 +5572,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>623709</v>
+        <v>623714</v>
       </c>
       <c r="R46" t="n">
-        <v>7310261</v>
+        <v>7310251</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5603,7 +5607,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5613,7 +5617,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5628,12 +5632,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5644,10 +5648,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135333629</v>
+        <v>135333626</v>
       </c>
       <c r="B47" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5655,21 +5659,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5682,7 +5686,7 @@
         <v>623753</v>
       </c>
       <c r="R47" t="n">
-        <v>7310283</v>
+        <v>7310291</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5714,7 +5718,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5724,7 +5728,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5755,7 +5759,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135336957</v>
+        <v>134456767</v>
       </c>
       <c r="B48" t="n">
         <v>79963</v>
@@ -5790,13 +5794,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623699</v>
+        <v>623900</v>
       </c>
       <c r="R48" t="n">
-        <v>7310215</v>
+        <v>7310120</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5820,22 +5824,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5850,26 +5854,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134456778</v>
+        <v>135331263</v>
       </c>
       <c r="B49" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5877,37 +5877,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623793</v>
+        <v>623731</v>
       </c>
       <c r="R49" t="n">
-        <v>7310206</v>
+        <v>7310280</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5931,22 +5931,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5961,22 +5961,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135330533</v>
+        <v>135333624</v>
       </c>
       <c r="B50" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5984,21 +5988,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6008,13 +6012,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623740</v>
+        <v>623709</v>
       </c>
       <c r="R50" t="n">
-        <v>7310280</v>
+        <v>7310261</v>
       </c>
       <c r="S50" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6043,7 +6047,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6053,7 +6057,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6068,12 +6072,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6084,10 +6088,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135336956</v>
+        <v>135333629</v>
       </c>
       <c r="B51" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6095,21 +6099,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6119,10 +6123,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623738</v>
+        <v>623753</v>
       </c>
       <c r="R51" t="n">
-        <v>7310208</v>
+        <v>7310283</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6154,7 +6158,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6164,7 +6168,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,12 +6183,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6195,10 +6199,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135336959</v>
+        <v>135336957</v>
       </c>
       <c r="B52" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6206,21 +6210,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6230,13 +6234,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>623723</v>
+        <v>623699</v>
       </c>
       <c r="R52" t="n">
-        <v>7310256</v>
+        <v>7310215</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6265,7 +6269,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6275,7 +6279,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6306,7 +6310,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135336964</v>
+        <v>134456778</v>
       </c>
       <c r="B53" t="n">
         <v>79396</v>
@@ -6341,13 +6345,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623808</v>
+        <v>623793</v>
       </c>
       <c r="R53" t="n">
-        <v>7310244</v>
+        <v>7310206</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6371,27 +6375,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>rikligt med soral</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6406,15 +6405,460 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135330533</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>623740</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S54" t="n">
+        <v>17</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135336956</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>623738</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7310208</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
           <t>Alva Danielsson</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>Alva Danielsson</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr">
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135336959</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>623723</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7310256</v>
+      </c>
+      <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135336964</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>623808</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7310244</v>
+      </c>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>rikligt med soral</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4520,10 +4520,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134456770</v>
+        <v>135358159</v>
       </c>
       <c r="B37" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4531,37 +4531,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623875</v>
+        <v>623777</v>
       </c>
       <c r="R37" t="n">
-        <v>7310171</v>
+        <v>7310175</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4585,22 +4585,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4615,19 +4615,23 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135333628</v>
+        <v>134456770</v>
       </c>
       <c r="B38" t="n">
         <v>78377</v>
@@ -4662,13 +4666,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623755</v>
+        <v>623875</v>
       </c>
       <c r="R38" t="n">
-        <v>7310283</v>
+        <v>7310171</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4692,22 +4696,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4722,26 +4726,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134456773</v>
+        <v>135333628</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,21 +4749,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623744</v>
+        <v>623755</v>
       </c>
       <c r="R39" t="n">
-        <v>7310162</v>
+        <v>7310283</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4803,27 +4803,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4838,19 +4833,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134456775</v>
+        <v>134456773</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4885,13 +4884,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>623790</v>
+        <v>623744</v>
       </c>
       <c r="R40" t="n">
-        <v>7310142</v>
+        <v>7310162</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4920,7 +4919,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4930,12 +4929,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gamla hackmärken i tall</t>
+          <t>Ringhack i tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4962,7 +4961,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135336954</v>
+        <v>134456775</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -4991,24 +4990,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>623782</v>
+        <v>623790</v>
       </c>
       <c r="R41" t="n">
-        <v>7310156</v>
+        <v>7310142</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5032,22 +5026,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla hackmärken i tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5062,23 +5061,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135336955</v>
+        <v>135336954</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -5109,7 +5104,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5118,13 +5113,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>623750</v>
+        <v>623782</v>
       </c>
       <c r="R42" t="n">
-        <v>7310194</v>
+        <v>7310156</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5153,7 +5148,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5163,7 +5158,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5194,7 +5189,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135336960</v>
+        <v>135336955</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -5234,13 +5229,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623741</v>
+        <v>623750</v>
       </c>
       <c r="R43" t="n">
-        <v>7310258</v>
+        <v>7310194</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5269,7 +5264,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5279,7 +5274,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5310,7 +5305,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135336965</v>
+        <v>135336960</v>
       </c>
       <c r="B44" t="n">
         <v>57975</v>
@@ -5350,13 +5345,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623813</v>
+        <v>623741</v>
       </c>
       <c r="R44" t="n">
-        <v>7310236</v>
+        <v>7310258</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,7 +5380,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5395,7 +5390,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5426,48 +5421,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135331264</v>
+        <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>623755</v>
+        <v>623813</v>
       </c>
       <c r="R45" t="n">
-        <v>7310300</v>
+        <v>7310236</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5521,12 +5521,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5537,48 +5537,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135330530</v>
+        <v>135331264</v>
       </c>
       <c r="B46" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>623714</v>
+        <v>623755</v>
       </c>
       <c r="R46" t="n">
-        <v>7310251</v>
+        <v>7310300</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5632,12 +5632,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5648,7 +5648,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135333626</v>
+        <v>135330530</v>
       </c>
       <c r="B47" t="n">
         <v>79131</v>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623753</v>
+        <v>623714</v>
       </c>
       <c r="R47" t="n">
-        <v>7310291</v>
+        <v>7310251</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5743,12 +5743,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5759,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134456767</v>
+        <v>135333626</v>
       </c>
       <c r="B48" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5770,21 +5770,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5794,13 +5794,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623900</v>
+        <v>623753</v>
       </c>
       <c r="R48" t="n">
-        <v>7310120</v>
+        <v>7310291</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5824,22 +5824,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5854,19 +5854,23 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135331263</v>
+        <v>134456767</v>
       </c>
       <c r="B49" t="n">
         <v>79963</v>
@@ -5897,17 +5901,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623731</v>
+        <v>623900</v>
       </c>
       <c r="R49" t="n">
-        <v>7310280</v>
+        <v>7310120</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5931,22 +5935,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5961,23 +5965,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135333624</v>
+        <v>135331263</v>
       </c>
       <c r="B50" t="n">
         <v>79963</v>
@@ -6008,14 +6008,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623709</v>
+        <v>623731</v>
       </c>
       <c r="R50" t="n">
-        <v>7310261</v>
+        <v>7310280</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,12 +6072,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6088,7 +6088,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135333629</v>
+        <v>135333624</v>
       </c>
       <c r="B51" t="n">
         <v>79963</v>
@@ -6123,10 +6123,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623753</v>
+        <v>623709</v>
       </c>
       <c r="R51" t="n">
-        <v>7310283</v>
+        <v>7310261</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6199,7 +6199,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135336957</v>
+        <v>135333629</v>
       </c>
       <c r="B52" t="n">
         <v>79963</v>
@@ -6234,13 +6234,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>623699</v>
+        <v>623753</v>
       </c>
       <c r="R52" t="n">
-        <v>7310215</v>
+        <v>7310283</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6294,12 +6294,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6310,10 +6310,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134456778</v>
+        <v>135336957</v>
       </c>
       <c r="B53" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6321,21 +6321,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623793</v>
+        <v>623699</v>
       </c>
       <c r="R53" t="n">
-        <v>7310206</v>
+        <v>7310215</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6375,22 +6375,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6405,19 +6405,23 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135330533</v>
+        <v>134456778</v>
       </c>
       <c r="B54" t="n">
         <v>79396</v>
@@ -6452,13 +6456,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>623740</v>
+        <v>623793</v>
       </c>
       <c r="R54" t="n">
-        <v>7310280</v>
+        <v>7310206</v>
       </c>
       <c r="S54" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6482,22 +6486,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6512,23 +6516,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135336956</v>
+        <v>135330533</v>
       </c>
       <c r="B55" t="n">
         <v>79396</v>
@@ -6563,13 +6563,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623738</v>
+        <v>623740</v>
       </c>
       <c r="R55" t="n">
-        <v>7310208</v>
+        <v>7310280</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6623,12 +6623,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6639,7 +6639,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135336959</v>
+        <v>135336956</v>
       </c>
       <c r="B56" t="n">
         <v>79396</v>
@@ -6674,13 +6674,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623723</v>
+        <v>623738</v>
       </c>
       <c r="R56" t="n">
-        <v>7310256</v>
+        <v>7310208</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6750,7 +6750,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135336964</v>
+        <v>135336959</v>
       </c>
       <c r="B57" t="n">
         <v>79396</v>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623808</v>
+        <v>623723</v>
       </c>
       <c r="R57" t="n">
-        <v>7310244</v>
+        <v>7310256</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6830,12 +6830,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>rikligt med soral</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6859,6 +6854,122 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135336964</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>623808</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7310244</v>
+      </c>
+      <c r="S58" t="n">
+        <v>9</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>rikligt med soral</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336951</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456768</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330529</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330532</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336962</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456772</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336961</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456771</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1980,6 +2040,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456774</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333617</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2202,6 +2272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333622</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2313,6 +2388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330534</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2424,6 +2504,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331260</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2535,6 +2620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331261</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2646,6 +2736,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333620</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2757,6 +2852,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333618</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2868,6 +2968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333623</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2979,6 +3084,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333630</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3086,6 +3196,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456779</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3197,6 +3312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333627</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3304,6 +3424,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456769</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3411,6 +3536,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456776</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3518,6 +3648,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456777</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3629,6 +3764,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330531</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3740,6 +3880,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333621</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3851,6 +3996,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333625</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3962,6 +4112,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333631</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4073,6 +4228,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333633</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4184,6 +4344,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333636</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4295,6 +4460,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336953</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4406,6 +4576,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336958</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4517,6 +4692,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336963</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4628,6 +4808,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358159</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4735,6 +4920,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456770</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4846,6 +5036,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333628</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4958,6 +5153,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456773</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5070,6 +5270,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456775</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5186,6 +5391,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336954</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5302,6 +5512,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336955</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5418,6 +5633,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336960</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5534,6 +5754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336965</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5645,6 +5870,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331264</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5756,6 +5986,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330530</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5867,6 +6102,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333626</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5974,6 +6214,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456767</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6085,6 +6330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331263</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6196,6 +6446,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333624</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6307,6 +6562,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333629</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6418,6 +6678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336957</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6525,6 +6790,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456778</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6636,6 +6906,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330533</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6747,6 +7022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336956</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6858,6 +7138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336959</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6974,8 +7259,72 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135336952</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135336951</v>
       </c>
       <c r="B4" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135330529</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135330532</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>135336962</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135336961</v>
       </c>
       <c r="B11" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>135333617</v>
       </c>
       <c r="B14" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>135333622</v>
       </c>
       <c r="B15" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>135330534</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>135331260</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>135331261</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>135333620</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135333618</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>135333623</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>135333630</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>135333627</v>
       </c>
       <c r="B24" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>135330531</v>
       </c>
       <c r="B28" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>135333621</v>
       </c>
       <c r="B29" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>135333625</v>
       </c>
       <c r="B30" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>135333631</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135333633</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>135333636</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>135336953</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135336958</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>135336963</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135358159</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>135333628</v>
       </c>
       <c r="B39" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>135336954</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>135336955</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>135336960</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>135331264</v>
       </c>
       <c r="B46" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135330530</v>
       </c>
       <c r="B47" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>135333626</v>
       </c>
       <c r="B48" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>135331263</v>
       </c>
       <c r="B50" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>135333624</v>
       </c>
       <c r="B51" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135333629</v>
       </c>
       <c r="B52" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>135336957</v>
       </c>
       <c r="B53" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>135330533</v>
       </c>
       <c r="B55" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>135336956</v>
       </c>
       <c r="B56" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>135336959</v>
       </c>
       <c r="B57" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135336964</v>
       </c>
       <c r="B58" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135336952</v>
       </c>
       <c r="B3" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135336951</v>
       </c>
       <c r="B4" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135330529</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135330532</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>135336962</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135336961</v>
       </c>
       <c r="B11" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>135333617</v>
       </c>
       <c r="B14" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>135333622</v>
       </c>
       <c r="B15" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>135330534</v>
       </c>
       <c r="B16" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>135331260</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>135331261</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>135333620</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>135333618</v>
       </c>
       <c r="B20" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>135333623</v>
       </c>
       <c r="B21" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>135333630</v>
       </c>
       <c r="B22" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>135333627</v>
       </c>
       <c r="B24" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>135330531</v>
       </c>
       <c r="B28" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>135333621</v>
       </c>
       <c r="B29" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>135333625</v>
       </c>
       <c r="B30" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>135333631</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135333633</v>
       </c>
       <c r="B32" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>135333636</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>135336953</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135336958</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>135336963</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135358159</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>135333628</v>
       </c>
       <c r="B39" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>135331264</v>
       </c>
       <c r="B46" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135330530</v>
       </c>
       <c r="B47" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>135333626</v>
       </c>
       <c r="B48" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>135331263</v>
       </c>
       <c r="B50" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>135333624</v>
       </c>
       <c r="B51" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135333629</v>
       </c>
       <c r="B52" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>135336957</v>
       </c>
       <c r="B53" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>135330533</v>
       </c>
       <c r="B55" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>135336956</v>
       </c>
       <c r="B56" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>135336959</v>
       </c>
       <c r="B57" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135336964</v>
       </c>
       <c r="B58" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134456766</v>
+        <v>135336952</v>
       </c>
       <c r="B3" t="n">
-        <v>79963</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623830</v>
+        <v>623805</v>
       </c>
       <c r="R3" t="n">
-        <v>7310041</v>
+        <v>7310020</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,49 +887,53 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456766</t>
+          <t>https://artportalen.se/Sighting/135336952</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134456768</v>
+        <v>135336951</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623900</v>
+        <v>623787</v>
       </c>
       <c r="R4" t="n">
-        <v>7310120</v>
+        <v>7310002</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +973,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +1003,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456768</t>
+          <t>https://artportalen.se/Sighting/135336951</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134456772</v>
+        <v>134456766</v>
       </c>
       <c r="B5" t="n">
-        <v>79452</v>
+        <v>79963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623724</v>
+        <v>623830</v>
       </c>
       <c r="R5" t="n">
-        <v>7310158</v>
+        <v>7310041</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,38 +1130,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456772</t>
+          <t>https://artportalen.se/Sighting/134456766</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134456771</v>
+        <v>134456768</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623825</v>
+        <v>623900</v>
       </c>
       <c r="R6" t="n">
-        <v>7310297</v>
+        <v>7310120</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1242,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456771</t>
+          <t>https://artportalen.se/Sighting/134456768</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134456774</v>
+        <v>135330529</v>
       </c>
       <c r="B7" t="n">
-        <v>83222</v>
+        <v>79107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623732</v>
+        <v>623697</v>
       </c>
       <c r="R7" t="n">
-        <v>7310148</v>
+        <v>7310241</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1313,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1343,31 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456774</t>
+          <t>https://artportalen.se/Sighting/135330529</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134456779</v>
+        <v>135330532</v>
       </c>
       <c r="B8" t="n">
-        <v>79130</v>
+        <v>79107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1399,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623810</v>
+        <v>623736</v>
       </c>
       <c r="R8" t="n">
-        <v>7310162</v>
+        <v>7310280</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1429,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,27 +1459,31 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456779</t>
+          <t>https://artportalen.se/Sighting/135330532</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134456769</v>
+        <v>135336962</v>
       </c>
       <c r="B9" t="n">
-        <v>79992</v>
+        <v>79107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1491,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1515,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623900</v>
+        <v>623775</v>
       </c>
       <c r="R9" t="n">
-        <v>7310143</v>
+        <v>7310254</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1545,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,27 +1575,31 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456769</t>
+          <t>https://artportalen.se/Sighting/135336962</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134456776</v>
+        <v>134456772</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>79452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1631,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623807</v>
+        <v>623724</v>
       </c>
       <c r="R10" t="n">
-        <v>7310160</v>
+        <v>7310158</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,16 +1702,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456776</t>
+          <t>https://artportalen.se/Sighting/134456772</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134456777</v>
+        <v>135336961</v>
       </c>
       <c r="B11" t="n">
-        <v>79992</v>
+        <v>81423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1743,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623758</v>
+        <v>623755</v>
       </c>
       <c r="R11" t="n">
-        <v>7310258</v>
+        <v>7310257</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1773,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,49 +1803,53 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456777</t>
+          <t>https://artportalen.se/Sighting/135336961</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134456770</v>
+        <v>134456771</v>
       </c>
       <c r="B12" t="n">
-        <v>78377</v>
+        <v>91988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1859,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623875</v>
+        <v>623825</v>
       </c>
       <c r="R12" t="n">
-        <v>7310171</v>
+        <v>7310297</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,16 +1930,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456770</t>
+          <t>https://artportalen.se/Sighting/134456771</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134456773</v>
+        <v>134456774</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>83222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1971,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623744</v>
+        <v>623732</v>
       </c>
       <c r="R13" t="n">
-        <v>7310162</v>
+        <v>7310148</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,12 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,16 +2042,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456773</t>
+          <t>https://artportalen.se/Sighting/134456774</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134456775</v>
+        <v>135333617</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>83292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2059,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,13 +2083,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623790</v>
+        <v>623762</v>
       </c>
       <c r="R14" t="n">
-        <v>7310142</v>
+        <v>7310114</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,27 +2113,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla hackmärken i tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,27 +2143,31 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456775</t>
+          <t>https://artportalen.se/Sighting/135333617</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134456767</v>
+        <v>135333622</v>
       </c>
       <c r="B15" t="n">
-        <v>79963</v>
+        <v>83292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,21 +2175,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,13 +2199,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623900</v>
+        <v>623739</v>
       </c>
       <c r="R15" t="n">
-        <v>7310120</v>
+        <v>7310146</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,22 +2229,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,49 +2259,53 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456767</t>
+          <t>https://artportalen.se/Sighting/135333622</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134456778</v>
+        <v>135330534</v>
       </c>
       <c r="B16" t="n">
-        <v>79396</v>
+        <v>92011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>260591</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,13 +2315,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623793</v>
+        <v>623725</v>
       </c>
       <c r="R16" t="n">
-        <v>7310206</v>
+        <v>7310245</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,22 +2345,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,18 +2375,4893 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330534</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135331260</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623814</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7310091</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331260</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135331261</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>623779</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7310157</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331261</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135333620</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>623771</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7310137</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333620</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135333618</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>623772</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7310131</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333618</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135333623</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>623707</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7310261</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333623</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135333630</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>623777</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7310269</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333630</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134456779</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>623810</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7310162</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456779</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135333627</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333627</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134456769</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7310143</v>
+      </c>
+      <c r="S25" t="n">
+        <v>14</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456769</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134456776</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>623807</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7310160</v>
+      </c>
+      <c r="S26" t="n">
+        <v>18</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456776</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134456777</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>623758</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7310258</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456777</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135330531</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>623713</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7310247</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330531</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135333621</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>623770</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7310168</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333621</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135333625</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>623754</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333625</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135333631</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>623776</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7310265</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333631</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135333633</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>623803</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333633</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135333636</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>623860</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7310128</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333636</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135336953</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>623790</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7310126</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336953</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135336958</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>623711</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7310252</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336958</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135336963</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>623802</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7310245</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336963</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135358159</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>623777</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7310175</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358159</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134456770</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>623875</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7310171</v>
+      </c>
+      <c r="S38" t="n">
+        <v>11</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456770</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135333628</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>623755</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333628</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134456773</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>623744</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7310162</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456773</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134456775</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>623790</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7310142</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla hackmärken i tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456775</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135336954</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>623782</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7310156</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336954</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135336955</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>623750</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7310194</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336955</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135336960</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>623741</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7310258</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336960</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135336965</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>623813</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7310236</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336965</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135331264</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>623755</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7310300</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331264</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135330530</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>623714</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330530</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135333626</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333626</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134456767</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7310120</v>
+      </c>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456767</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135331263</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>623731</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331263</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135333624</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>623709</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7310261</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333624</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135333629</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333629</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135336957</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>623699</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7310215</v>
+      </c>
+      <c r="S53" t="n">
+        <v>8</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336957</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134456778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>623793</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7310206</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134456778</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135330533</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>623740</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S55" t="n">
+        <v>17</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330533</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135336956</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>623738</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7310208</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336956</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135336959</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>623723</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7310256</v>
+      </c>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336959</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135336964</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>623808</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7310244</v>
+      </c>
+      <c r="S58" t="n">
+        <v>9</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>rikligt med soral</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336964</t>
         </is>
       </c>
     </row>
@@ -2385,6 +7282,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>135336951</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>135330534</v>
       </c>
       <c r="B16" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>135331264</v>
       </c>
       <c r="B46" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
